--- a/artfynd/A 21732-2026 artfynd.xlsx
+++ b/artfynd/A 21732-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134216907</v>
+        <v>134216900</v>
       </c>
       <c r="B2" t="n">
-        <v>91977</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,33 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brattfäbodberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753020</v>
+        <v>752799</v>
       </c>
       <c r="R2" t="n">
-        <v>7107535</v>
+        <v>7107614</v>
       </c>
       <c r="S2" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -751,14 +760,19 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -778,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134216900</v>
+        <v>134216907</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>91977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,42 +803,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brattfäbodberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752799</v>
+        <v>753020</v>
       </c>
       <c r="R3" t="n">
-        <v>7107614</v>
+        <v>7107535</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,7 +858,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,19 +868,14 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hackmärken från födosök</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134216908</v>
+        <v>134216910</v>
       </c>
       <c r="B6" t="n">
-        <v>91957</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,37 +1125,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brattfäbodberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752953</v>
+        <v>752926</v>
       </c>
       <c r="R6" t="n">
-        <v>7107517</v>
+        <v>7107565</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1194,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134216910</v>
+        <v>134216908</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>91957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1232,42 +1237,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brattfäbodberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752926</v>
+        <v>752953</v>
       </c>
       <c r="R7" t="n">
-        <v>7107565</v>
+        <v>7107517</v>
       </c>
       <c r="S7" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 21732-2026 artfynd.xlsx
+++ b/artfynd/A 21732-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134216900</v>
+        <v>134216907</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>91977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brattfäbodberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752799</v>
+        <v>753020</v>
       </c>
       <c r="R2" t="n">
-        <v>7107614</v>
+        <v>7107535</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +741,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,19 +751,14 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackmärken från födosök</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -792,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134216907</v>
+        <v>134216900</v>
       </c>
       <c r="B3" t="n">
-        <v>91977</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,33 +789,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brattfäbodberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753020</v>
+        <v>752799</v>
       </c>
       <c r="R3" t="n">
-        <v>7107535</v>
+        <v>7107614</v>
       </c>
       <c r="S3" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -868,14 +863,19 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 21732-2026 artfynd.xlsx
+++ b/artfynd/A 21732-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134216907</v>
+        <v>134216900</v>
       </c>
       <c r="B2" t="n">
-        <v>91977</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,33 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brattfäbodberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753020</v>
+        <v>752799</v>
       </c>
       <c r="R2" t="n">
-        <v>7107535</v>
+        <v>7107614</v>
       </c>
       <c r="S2" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -751,14 +760,19 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -778,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134216900</v>
+        <v>134216907</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>91979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,42 +803,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brattfäbodberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752799</v>
+        <v>753020</v>
       </c>
       <c r="R3" t="n">
-        <v>7107614</v>
+        <v>7107535</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,7 +858,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,19 +868,14 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hackmärken från födosök</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -898,7 +898,7 @@
         <v>134216904</v>
       </c>
       <c r="B4" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>134216908</v>
       </c>
       <c r="B7" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>134216903</v>
       </c>
       <c r="B9" t="n">
-        <v>89338</v>
+        <v>89339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21732-2026 artfynd.xlsx
+++ b/artfynd/A 21732-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134216900</v>
+        <v>134216907</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>91980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brattfäbodberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752799</v>
+        <v>753020</v>
       </c>
       <c r="R2" t="n">
-        <v>7107614</v>
+        <v>7107535</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +741,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,19 +751,14 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackmärken från födosök</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -792,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134216907</v>
+        <v>134216900</v>
       </c>
       <c r="B3" t="n">
-        <v>91980</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,33 +789,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brattfäbodberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753020</v>
+        <v>752799</v>
       </c>
       <c r="R3" t="n">
-        <v>7107535</v>
+        <v>7107614</v>
       </c>
       <c r="S3" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -868,14 +863,19 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 21732-2026 artfynd.xlsx
+++ b/artfynd/A 21732-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134216907</v>
       </c>
       <c r="B2" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>134216904</v>
       </c>
       <c r="B4" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>134216908</v>
       </c>
       <c r="B7" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>134216903</v>
       </c>
       <c r="B9" t="n">
-        <v>89340</v>
+        <v>89347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21732-2026 artfynd.xlsx
+++ b/artfynd/A 21732-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134216907</v>
+        <v>134216903</v>
       </c>
       <c r="B2" t="n">
-        <v>91987</v>
+        <v>89354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753020</v>
+        <v>752968</v>
       </c>
       <c r="R2" t="n">
-        <v>7107535</v>
+        <v>7107446</v>
       </c>
       <c r="S2" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -751,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134216900</v>
+        <v>134216904</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brattfäbodberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752799</v>
+        <v>752956</v>
       </c>
       <c r="R3" t="n">
-        <v>7107614</v>
+        <v>7107442</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,19 +862,14 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hackmärken från födosök</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -895,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134216904</v>
+        <v>134216908</v>
       </c>
       <c r="B4" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752956</v>
+        <v>752953</v>
       </c>
       <c r="R4" t="n">
-        <v>7107442</v>
+        <v>7107517</v>
       </c>
       <c r="S4" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134216902</v>
+        <v>134216910</v>
       </c>
       <c r="B5" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,27 +1007,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1042,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752950</v>
+        <v>752926</v>
       </c>
       <c r="R5" t="n">
-        <v>7107414</v>
+        <v>7107565</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1087,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134216910</v>
+        <v>134216900</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,16 +1119,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1154,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752926</v>
+        <v>752799</v>
       </c>
       <c r="R6" t="n">
-        <v>7107565</v>
+        <v>7107614</v>
       </c>
       <c r="S6" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,14 +1193,19 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1226,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134216908</v>
+        <v>134216909</v>
       </c>
       <c r="B7" t="n">
-        <v>91967</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,34 +1236,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brattfäbodberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752953</v>
+        <v>752945</v>
       </c>
       <c r="R7" t="n">
-        <v>7107517</v>
+        <v>7107523</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1296,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1306,14 +1310,19 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack från födosök</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1333,38 +1342,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134216909</v>
+        <v>134216902</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1373,13 +1382,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752945</v>
+        <v>752950</v>
       </c>
       <c r="R8" t="n">
-        <v>7107523</v>
+        <v>7107414</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1418,19 +1427,14 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack från födosök</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1447,113 +1451,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>134216903</v>
-      </c>
-      <c r="B9" t="n">
-        <v>89347</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>510</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Doftskinn</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Cystostereum murrayi</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Brattfäbodberget, Vb</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>752968</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7107446</v>
-      </c>
-      <c r="S9" t="n">
-        <v>26</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21732-2026 artfynd.xlsx
+++ b/artfynd/A 21732-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134216903</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134216904</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134216908</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134216910</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134216900</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134216909</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,8 +1486,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134216902</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>